--- a/tracking/suivi-leads-klynera.xlsx
+++ b/tracking/suivi-leads-klynera.xlsx
@@ -5627,6 +5627,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -5728,7 +5729,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Nettoyage automobile</t>
+          <t>Nettoyage de bureaux</t>
         </is>
       </c>
       <c r="E8" s="4">
@@ -5825,6 +5826,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
